--- a/Services.xlsx
+++ b/Services.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22A4B5E6-A099-4FCD-AE39-EE6EB680ED5E}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17AD8C5D-0B5F-4460-B2D4-138898A32711}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
   <si>
     <t>slug</t>
   </si>
@@ -53,15 +53,9 @@
     <t>description</t>
   </si>
   <si>
-    <t>hvac-tuneup</t>
-  </si>
-  <si>
     <t>hvac-repair</t>
   </si>
   <si>
-    <t>fiber-sedan</t>
-  </si>
-  <si>
     <t>HVAC Repair</t>
   </si>
   <si>
@@ -71,18 +65,12 @@
     <t>HVAC_IMG_4.JPG</t>
   </si>
   <si>
-    <t>HVAC_IMG_2.jpeg</t>
-  </si>
-  <si>
     <t>Seasonal maintenance to keep your system efficient, safe, and reliable</t>
   </si>
   <si>
     <t>Fast, expert diagnostics and transparent pricing for needed fixes</t>
   </si>
   <si>
-    <t>Star-ceiling headliner with RGBW twinkle &amp; music-sync. Professional install</t>
-  </si>
-  <si>
     <t>hvac-install Proposal</t>
   </si>
   <si>
@@ -98,40 +86,12 @@
     <t>Professional on-site assessment of your home or business;Equipment options tailored to space, budget, and comfort goals;Clear installation plan and timeline</t>
   </si>
   <si>
-    <t>RGBW light engine with app + remote control (solid colors &amp; effects).;
-Twinkle / meteor modes and optional music-sync animations.;
-Hundreds of fiber strands installed for dense, even star coverage.;
-Hidden wiring and fused power with OEM-style protection.;
-Install typically completed in 2 days for sedans (vehicle-dependent).;
-Warranty on workmanship.</t>
-  </si>
-  <si>
-    <t>Skilled technician diagnoses issue &amp; explains options;Up-front pricing by repair, no hidden fees;Diagnostic fee due at scheduling; often credited if repair proceeds;Limited 1–5 year warranty depending on repair type</t>
-  </si>
-  <si>
-    <t>Thermostat check &amp; calibration;Tighten electrical connections; verify motor volts/amps;Lubricate movingClean/inspect coils; clear condensate drain parts where applicable;Check refrigerant level; inspect for leaks;Replace/inspect air filter; verify airflow;Safety checks (gas pressure, heat exchanger, CO)</t>
-  </si>
-  <si>
-    <t>fiber-suv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGBW light engine with app + remote control (solid colors &amp; effects).;
-Twinkle / meteor modes and optional music-sync animations.;
-Hundreds of fiber strands installed for dense, even star coverage.;
-Hidden wiring and fused power with OEM-style protection.;
-Install typically completed in 2 days for sedans (vehicle-dependent).;
-Warranty on workmanship. </t>
-  </si>
-  <si>
     <t>sales price</t>
   </si>
   <si>
     <t>bullet points</t>
   </si>
   <si>
-    <t>IMG_1353.jpg</t>
-  </si>
-  <si>
     <t>actionType</t>
   </si>
   <si>
@@ -156,16 +116,58 @@
     <t>If you don’t see a service that matches your needs, select this option and our team will review your request to let you know how we can help</t>
   </si>
   <si>
-    <t>Cramer-Logo.png</t>
-  </si>
-  <si>
     <t>Flooring.jpeg</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiber Optic Lights Sedan Proposal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiber Optic Lights SUV Proposal </t>
+    <t>Furnace-tuneup</t>
+  </si>
+  <si>
+    <t>AC-tuneup</t>
+  </si>
+  <si>
+    <t>Clean condensate drain parts;Check refrigerant level; Replace/Install Air Filter; Clean interior and exterior coils; Clean blower componets; Insepect electrical componenets</t>
+  </si>
+  <si>
+    <t>Inspection of electrical connections; Replace/inspect air filter; Safety checks; Inspect/Clean burners; Inspect and clean blower motor;</t>
+  </si>
+  <si>
+    <t>Skilled technician diagnoses issue &amp; explains options;Up-front pricing by repair;Diagnostic fee due at scheduling; Fee is credited if repair proceeds;Limited 0–5 year warranty depending on the scope of work</t>
+  </si>
+  <si>
+    <t>CramerLogoText.png</t>
+  </si>
+  <si>
+    <t>Hot-Water-Tank-Proposal</t>
+  </si>
+  <si>
+    <t>Hot Water Tank Proposal</t>
+  </si>
+  <si>
+    <t>Professional on-site assessment of your home or business;Equipment options tailored to space, budget, and comfort goals;Professional Installation;5 year warranty;Clear installation plan and timeline</t>
+  </si>
+  <si>
+    <t>Light-Fixture-Replacment-and-Install</t>
+  </si>
+  <si>
+    <t>Light Fixture Replacment/ install</t>
+  </si>
+  <si>
+    <t>Professional on-site assessment of your home or business;Fixture options tailored to space, budget, and comfort goals;Professional Installation;5 year warranty;Clear installation plan and timeline</t>
+  </si>
+  <si>
+    <t>General Repair</t>
+  </si>
+  <si>
+    <t>General-Repair</t>
+  </si>
+  <si>
+    <t>HVAC_IMG_2.JPG</t>
+  </si>
+  <si>
+    <t>WaterHeater.JPG</t>
+  </si>
+  <si>
+    <t>LightFixture.JPG</t>
   </si>
 </sst>
 </file>
@@ -553,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1357D1-FF94-4D48-8DFF-B0D3FC445256}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -577,7 +579,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -586,193 +588,229 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2">
         <v>75</v>
       </c>
       <c r="D2" s="2">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2">
         <v>150</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17AD8C5D-0B5F-4460-B2D4-138898A32711}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DD1FFC-AD37-4191-BB1F-2DD45101393B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
   <si>
     <t>slug</t>
   </si>
@@ -59,9 +59,6 @@
     <t>HVAC Repair</t>
   </si>
   <si>
-    <t>HVAC Tune-Up</t>
-  </si>
-  <si>
     <t>HVAC_IMG_4.JPG</t>
   </si>
   <si>
@@ -168,6 +165,18 @@
   </si>
   <si>
     <t>LightFixture.JPG</t>
+  </si>
+  <si>
+    <t>Furnace Tuneup</t>
+  </si>
+  <si>
+    <t>AC Tuneup</t>
+  </si>
+  <si>
+    <t>Furnace.JPG</t>
+  </si>
+  <si>
+    <t>Call us today, tell us your needs, and our team will provide the reliable support you’re looking for.</t>
   </si>
 </sst>
 </file>
@@ -579,7 +588,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -588,18 +597,18 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
         <v>75</v>
@@ -608,24 +617,24 @@
         <v>125</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2">
         <v>85</v>
@@ -634,16 +643,16 @@
         <v>150</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
@@ -658,158 +667,158 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DD1FFC-AD37-4191-BB1F-2DD45101393B}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D8B290-B964-4672-ABA0-3C8B543DA149}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
+    <workbookView xWindow="930" yWindow="1185" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>Skilled technician diagnoses issue &amp; explains options;Up-front pricing by repair;Diagnostic fee due at scheduling; Fee is credited if repair proceeds;Limited 0–5 year warranty depending on the scope of work</t>
   </si>
   <si>
-    <t>CramerLogoText.png</t>
-  </si>
-  <si>
     <t>Hot-Water-Tank-Proposal</t>
   </si>
   <si>
@@ -177,6 +174,9 @@
   </si>
   <si>
     <t>Call us today, tell us your needs, and our team will provide the reliable support you’re looking for.</t>
+  </si>
+  <si>
+    <t>CramerLogo&amp;Name 30, 2025, 02_50_59 PM.png</t>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2">
         <v>75</v>
@@ -634,7 +634,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2">
         <v>85</v>
@@ -643,7 +643,7 @@
         <v>150</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -667,7 +667,7 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>9</v>
@@ -715,13 +715,13 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>18</v>
@@ -753,23 +753,23 @@
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>18</v>
@@ -777,39 +777,39 @@
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D8B290-B964-4672-ABA0-3C8B543DA149}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BF3D5C-F28A-4863-9174-4651CFDFF465}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1185" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,12 +101,6 @@
     <t>Free</t>
   </si>
   <si>
-    <t>VInal Flooring Proposal</t>
-  </si>
-  <si>
-    <t>Vinal-Flooring-Proposal</t>
-  </si>
-  <si>
     <t>Professional on-site measurement and evaluation of your flooring space;Product options tailored to design preferences, durability needs, and budget;Clear installation plan, timeline, and transparent cost estimate</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
     <t>Light-Fixture-Replacment-and-Install</t>
   </si>
   <si>
-    <t>Light Fixture Replacment/ install</t>
-  </si>
-  <si>
     <t>Professional on-site assessment of your home or business;Fixture options tailored to space, budget, and comfort goals;Professional Installation;5 year warranty;Clear installation plan and timeline</t>
   </si>
   <si>
@@ -177,6 +168,15 @@
   </si>
   <si>
     <t>CramerLogo&amp;Name 30, 2025, 02_50_59 PM.png</t>
+  </si>
+  <si>
+    <t>Vinyl-Flooring-Proposal</t>
+  </si>
+  <si>
+    <t>Vinyl Flooring Proposal</t>
+  </si>
+  <si>
+    <t>Light Fixture Replacement/ install</t>
   </si>
 </sst>
 </file>
@@ -605,10 +605,10 @@
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2">
         <v>75</v>
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>18</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2">
         <v>85</v>
@@ -643,13 +643,13 @@
         <v>150</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -667,13 +667,13 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -715,13 +715,13 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>18</v>
@@ -729,23 +729,23 @@
     </row>
     <row r="7" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>18</v>
@@ -753,23 +753,23 @@
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>18</v>
@@ -777,22 +777,22 @@
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
@@ -800,22 +800,22 @@
     </row>
     <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>18</v>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="8_{88C0F26A-CD20-4CD1-B45D-F2DD193A6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BF3D5C-F28A-4863-9174-4651CFDFF465}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4193215-5FAB-478B-9F6F-B667216F50DA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
+    <workbookView xWindow="-105" yWindow="90" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>slug</t>
   </si>
@@ -68,12 +68,6 @@
     <t>Fast, expert diagnostics and transparent pricing for needed fixes</t>
   </si>
   <si>
-    <t>hvac-install Proposal</t>
-  </si>
-  <si>
-    <t>HVAC Install Proposal</t>
-  </si>
-  <si>
     <t>HVAC_IMG_3.JPG</t>
   </si>
   <si>
@@ -95,66 +89,21 @@
     <t>contact</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Free</t>
-  </si>
-  <si>
-    <t>Professional on-site measurement and evaluation of your flooring space;Product options tailored to design preferences, durability needs, and budget;Clear installation plan, timeline, and transparent cost estimate</t>
-  </si>
-  <si>
-    <t>If you don’t see a service that matches your needs, select this option and our team will review your request to let you know how we can help</t>
-  </si>
-  <si>
-    <t>Flooring.jpeg</t>
-  </si>
-  <si>
     <t>Furnace-tuneup</t>
   </si>
   <si>
     <t>AC-tuneup</t>
   </si>
   <si>
-    <t>Clean condensate drain parts;Check refrigerant level; Replace/Install Air Filter; Clean interior and exterior coils; Clean blower componets; Insepect electrical componenets</t>
-  </si>
-  <si>
     <t>Inspection of electrical connections; Replace/inspect air filter; Safety checks; Inspect/Clean burners; Inspect and clean blower motor;</t>
   </si>
   <si>
     <t>Skilled technician diagnoses issue &amp; explains options;Up-front pricing by repair;Diagnostic fee due at scheduling; Fee is credited if repair proceeds;Limited 0–5 year warranty depending on the scope of work</t>
   </si>
   <si>
-    <t>Hot-Water-Tank-Proposal</t>
-  </si>
-  <si>
-    <t>Hot Water Tank Proposal</t>
-  </si>
-  <si>
-    <t>Professional on-site assessment of your home or business;Equipment options tailored to space, budget, and comfort goals;Professional Installation;5 year warranty;Clear installation plan and timeline</t>
-  </si>
-  <si>
-    <t>Light-Fixture-Replacment-and-Install</t>
-  </si>
-  <si>
-    <t>Professional on-site assessment of your home or business;Fixture options tailored to space, budget, and comfort goals;Professional Installation;5 year warranty;Clear installation plan and timeline</t>
-  </si>
-  <si>
-    <t>General Repair</t>
-  </si>
-  <si>
-    <t>General-Repair</t>
-  </si>
-  <si>
     <t>HVAC_IMG_2.JPG</t>
   </si>
   <si>
-    <t>WaterHeater.JPG</t>
-  </si>
-  <si>
-    <t>LightFixture.JPG</t>
-  </si>
-  <si>
     <t>Furnace Tuneup</t>
   </si>
   <si>
@@ -164,26 +113,131 @@
     <t>Furnace.JPG</t>
   </si>
   <si>
-    <t>Call us today, tell us your needs, and our team will provide the reliable support you’re looking for.</t>
-  </si>
-  <si>
-    <t>CramerLogo&amp;Name 30, 2025, 02_50_59 PM.png</t>
-  </si>
-  <si>
-    <t>Vinyl-Flooring-Proposal</t>
-  </si>
-  <si>
-    <t>Vinyl Flooring Proposal</t>
-  </si>
-  <si>
-    <t>Light Fixture Replacement/ install</t>
+    <t>hvac-install Estimate</t>
+  </si>
+  <si>
+    <t>Mini-Spit-Install-Estimate</t>
+  </si>
+  <si>
+    <t>Mini Spit Install Estimate</t>
+  </si>
+  <si>
+    <t>Mini-Spit-Repair-Estimate</t>
+  </si>
+  <si>
+    <t>Mini Spit Repair Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermostat repair and installs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermostat-repair-&amp;-installs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat Pump Installation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat-Pump-Installation </t>
+  </si>
+  <si>
+    <t>Air Purifier &amp; Filtration Systems</t>
+  </si>
+  <si>
+    <t>Air-Purifier-&amp;-Filtration-Systems</t>
+  </si>
+  <si>
+    <t>Humidifiers &amp; Dehumidifiers</t>
+  </si>
+  <si>
+    <t>Humidifiers-&amp;-Dehumidifiers</t>
+  </si>
+  <si>
+    <t>Duct Sealing / Replacement</t>
+  </si>
+  <si>
+    <t>Duct-Sealing-/-Replacement</t>
+  </si>
+  <si>
+    <t>System Inspections</t>
+  </si>
+  <si>
+    <t>Efficiency Testing</t>
+  </si>
+  <si>
+    <t>System-Inspections</t>
+  </si>
+  <si>
+    <t>Efficiency-Testing</t>
+  </si>
+  <si>
+    <t>Cramer-Logo.png</t>
+  </si>
+  <si>
+    <t>Clean condensate drain parts;Check refrigerant level; Replace/Install Air Filter; Clean interior and exterior coils; Clean blower components; Inspect electrical components</t>
+  </si>
+  <si>
+    <t>HVAC Install Estimate</t>
+  </si>
+  <si>
+    <t>Professional installation of single-zone or multi-zone ductless mini-split systems.</t>
+  </si>
+  <si>
+    <t>Mount indoor wall unit; Set outdoor condenser; Run refrigerant and condensate lines; Vacuum and charge system; Test electrical connections; Calibrate remote or smart controller.</t>
+  </si>
+  <si>
+    <t>Diagnostic and repair services for malfunctioning ductless systems.</t>
+  </si>
+  <si>
+    <t>Inspect refrigerant lines for leaks; Check inverter board and fan motors; Test communication cables; Clean air filters and coils; Replace defective sensors or drain pumps; Verify proper refrigerant charge.</t>
+  </si>
+  <si>
+    <t>Replacement or installation of programmable and smart thermostats to improve comfort and efficiency.</t>
+  </si>
+  <si>
+    <t>Remove old thermostat; Inspect and label wiring; Install new base and connect wires; Configure heating/cooling programs; Connect to Wi-Fi; Test system operation.</t>
+  </si>
+  <si>
+    <t>Installation of high-efficiency heat pumps for year-round heating and cooling.</t>
+  </si>
+  <si>
+    <t>Set outdoor and indoor units; Connect refrigerant lines; Seal and insulate ducts; Wire defrost and control board; Charge system; Test heating and cooling cycles; Verify reversing valve function.</t>
+  </si>
+  <si>
+    <t>Installation of whole-home filtration or purification systems to improve indoor air quality.</t>
+  </si>
+  <si>
+    <t>Assess ductwork compatibility; Install purifier housing and filter; Connect electrical supply; Seal duct joints; Test airflow; Measure indoor air quality improvement.</t>
+  </si>
+  <si>
+    <t>Maintain balanced indoor humidity levels to enhance comfort and protect property.</t>
+  </si>
+  <si>
+    <t>Mount unit on supply or return duct; Connect water line and drain; Wire to control board; Adjust humidity settings; Test operation; Inspect for leaks or clogs.</t>
+  </si>
+  <si>
+    <t>Repair or replace damaged air ducts to restore airflow and energy efficiency</t>
+  </si>
+  <si>
+    <t>Inspect for leaks or crushed sections; Remove damaged ductwork; Install new flexible or rigid ducts; Apply mastic sealant; Wrap with insulation; Verify balanced airflow.</t>
+  </si>
+  <si>
+    <t>Comprehensive system checks to ensure safe and efficient operation</t>
+  </si>
+  <si>
+    <t>Inspect electrical components; Check refrigerant level; Measure temperature differentials; Test safety controls; Inspect blower and fan motors; Review system efficiency report</t>
+  </si>
+  <si>
+    <t>Detailed performance evaluation of your HVAC system to identify energy loss, optimize output, and lower utility costs</t>
+  </si>
+  <si>
+    <t>Measure airflow and static pressure; Check temperature differential; Verify refrigerant charge; Test electrical draw and amperage; Inspect duct insulation; Review SEER/AFUE performance ratings; Provide efficiency improvement recommendations</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +248,12 @@
     <font>
       <sz val="8"/>
       <color rgb="FF1B1F24"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -218,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,6 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1357D1-FF94-4D48-8DFF-B0D3FC445256}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -588,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -597,24 +658,24 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -623,36 +684,36 @@
         <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2">
         <v>150</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
@@ -663,162 +724,251 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
+      <c r="C9" s="2">
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10">
-        <v>100</v>
+      <c r="C10" s="2">
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>18</v>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4193215-5FAB-478B-9F6F-B667216F50DA}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2C06E7C-B1F4-4A3E-8A35-12F19FC03985}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="90" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>Efficiency-Testing</t>
   </si>
   <si>
-    <t>Cramer-Logo.png</t>
-  </si>
-  <si>
     <t>Clean condensate drain parts;Check refrigerant level; Replace/Install Air Filter; Clean interior and exterior coils; Clean blower components; Inspect electrical components</t>
   </si>
   <si>
@@ -231,6 +228,9 @@
   </si>
   <si>
     <t>Measure airflow and static pressure; Check temperature differential; Verify refrigerant charge; Test electrical draw and amperage; Inspect duct insulation; Review SEER/AFUE performance ratings; Provide efficiency improvement recommendations</t>
+  </si>
+  <si>
+    <t>CramerLogoText.png</t>
   </si>
 </sst>
 </file>
@@ -684,7 +684,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>16</v>
@@ -745,7 +745,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -775,13 +775,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
@@ -798,13 +798,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>16</v>
@@ -821,13 +821,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>16</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>16</v>
@@ -867,13 +867,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>16</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>16</v>
@@ -913,13 +913,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>16</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>16</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>16</v>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2C06E7C-B1F4-4A3E-8A35-12F19FC03985}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677B0139-3FE9-4756-A5D2-3DABDB93388F}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="90" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>slug</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>CramerLogoText.png</t>
+  </si>
+  <si>
+    <t>CramerLogo&amp;Name 30, 2025, 02_50_59 PM.png</t>
   </si>
 </sst>
 </file>
@@ -764,7 +767,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -775,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>46</v>
@@ -787,7 +790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -798,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -821,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>50</v>

--- a/Services.xlsx
+++ b/Services.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ce8c4294ab9a41e/Desktop/Cramer Services html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677B0139-3FE9-4756-A5D2-3DABDB93388F}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{61B132E4-F11D-454B-B5DD-BD90BEFA91B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC4863B-EA99-40BD-84BC-4B231C66E5BD}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="90" windowWidth="23970" windowHeight="12750" xr2:uid="{23803704-7499-4AE1-8879-84F357FDE795}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>slug</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>Measure airflow and static pressure; Check temperature differential; Verify refrigerant charge; Test electrical draw and amperage; Inspect duct insulation; Review SEER/AFUE performance ratings; Provide efficiency improvement recommendations</t>
-  </si>
-  <si>
-    <t>CramerLogoText.png</t>
   </si>
   <si>
     <t>CramerLogo&amp;Name 30, 2025, 02_50_59 PM.png</t>
@@ -778,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>46</v>
@@ -801,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -824,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>50</v>
@@ -836,7 +833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -882,7 +879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -905,7 +902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -928,7 +925,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
